--- a/Apostas_Diarias/Apostas_20260503.xlsx
+++ b/Apostas_Diarias/Apostas_20260503.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_2B590F4F95B64B44B162D9F050B5187451BDFE2A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83091D6E-3AF6-414E-BB54-7CB5CD62F6B6}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_2B590F4F95B64B44B162D9F050B5187451BDFE2A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32E34ABB-9FDA-47E3-BBA5-403194D62FA1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -169,6 +169,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -456,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -750,6 +754,22 @@
         <v>1</v>
       </c>
     </row>
+    <row r="17" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="H17">
+        <f>48/3</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G20">
+        <f>24-16</f>
+        <v>8</v>
+      </c>
+      <c r="J20">
+        <f>34-8</f>
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
